--- a/artfynd/A 38234-2025 artfynd.xlsx
+++ b/artfynd/A 38234-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127796848</v>
       </c>
       <c r="B2" t="n">
-        <v>79609</v>
+        <v>79612</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127796935</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>127797054</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>127797105</v>
       </c>
       <c r="B5" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>127796731</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>127797553</v>
       </c>
       <c r="B7" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>127797231</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 38234-2025 artfynd.xlsx
+++ b/artfynd/A 38234-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127796848</v>
       </c>
       <c r="B2" t="n">
-        <v>79612</v>
+        <v>79618</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127796935</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>127797054</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>127797105</v>
       </c>
       <c r="B5" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>127796731</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>127797553</v>
       </c>
       <c r="B7" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>127797231</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 38234-2025 artfynd.xlsx
+++ b/artfynd/A 38234-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127796848</v>
       </c>
       <c r="B2" t="n">
-        <v>79618</v>
+        <v>79621</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127796935</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>127797054</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>127797105</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>78791</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>127796731</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>127797553</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>78791</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>127797231</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 38234-2025 artfynd.xlsx
+++ b/artfynd/A 38234-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127796848</v>
       </c>
       <c r="B2" t="n">
-        <v>79621</v>
+        <v>79673</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127796935</v>
       </c>
       <c r="B3" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>127797054</v>
       </c>
       <c r="B4" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>127797105</v>
       </c>
       <c r="B5" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>127796731</v>
       </c>
       <c r="B6" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>127797553</v>
       </c>
       <c r="B7" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>127797231</v>
       </c>
       <c r="B8" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,6 +1366,3086 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128486152</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>467326</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6867404</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128484618</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78840</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>467370</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6867567</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128484488</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78840</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>467296</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6867571</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128485668</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>467380</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6867346</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128484498</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78841</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>467297</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6867574</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128486130</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>467340</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6867393</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128485709</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78749</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>353</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>467387</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6867345</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128485715</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>467371</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6867346</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128484758</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>467386</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6867534</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128486214</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78841</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>467336</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6867418</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128485871</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>467353</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6867298</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128486103</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>467340</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6867371</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128484929</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78749</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>353</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>467411</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6867573</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128484624</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78841</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>467372</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6867560</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128486029</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>467343</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6867360</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128485651</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>467382</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6867360</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128486074</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>467329</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6867367</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128485883</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>467348</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6867319</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128484700</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>467385</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6867556</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128486009</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>467344</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6867344</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128485750</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>467374</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6867328</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128518797</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78749</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>353</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>467714</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6867283</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128518939</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78749</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>353</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>467658</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6867254</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128519134</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78841</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>467662</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6867285</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128519551</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79673</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>467578</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6867346</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128518723</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57845</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>467737</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6867274</v>
+      </c>
+      <c r="S34" t="n">
+        <v>50</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Läten noterade.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128520449</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78841</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>467349</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6867637</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128518707</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78749</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>353</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>467737</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6867274</v>
+      </c>
+      <c r="S36" t="n">
+        <v>20</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128518947</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79673</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>467644</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6867258</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128519150</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79673</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>467663</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6867282</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128519428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lassbodberget, Lassbodberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>467584</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6867351</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38234-2025 artfynd.xlsx
+++ b/artfynd/A 38234-2025 artfynd.xlsx
@@ -1872,10 +1872,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128486130</v>
+        <v>128485709</v>
       </c>
       <c r="B14" t="n">
-        <v>79083</v>
+        <v>78749</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467340</v>
+        <v>467387</v>
       </c>
       <c r="R14" t="n">
-        <v>6867393</v>
+        <v>6867345</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,10 +1969,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128485709</v>
+        <v>128486130</v>
       </c>
       <c r="B15" t="n">
-        <v>78749</v>
+        <v>79083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1980,21 +1980,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467387</v>
+        <v>467340</v>
       </c>
       <c r="R15" t="n">
-        <v>6867345</v>
+        <v>6867393</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2569,10 +2569,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128484929</v>
+        <v>128484624</v>
       </c>
       <c r="B21" t="n">
-        <v>78749</v>
+        <v>78841</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2580,21 +2580,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467411</v>
+        <v>467372</v>
       </c>
       <c r="R21" t="n">
-        <v>6867573</v>
+        <v>6867560</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2666,10 +2666,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128484624</v>
+        <v>128484929</v>
       </c>
       <c r="B22" t="n">
-        <v>78841</v>
+        <v>78749</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2677,21 +2677,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467372</v>
+        <v>467411</v>
       </c>
       <c r="R22" t="n">
-        <v>6867560</v>
+        <v>6867573</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3566,10 +3566,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128518939</v>
+        <v>128519134</v>
       </c>
       <c r="B31" t="n">
-        <v>78749</v>
+        <v>78841</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3577,21 +3577,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467658</v>
+        <v>467662</v>
       </c>
       <c r="R31" t="n">
-        <v>6867254</v>
+        <v>6867285</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3663,10 +3663,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128519134</v>
+        <v>128518939</v>
       </c>
       <c r="B32" t="n">
-        <v>78841</v>
+        <v>78749</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3674,21 +3674,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467662</v>
+        <v>467658</v>
       </c>
       <c r="R32" t="n">
-        <v>6867285</v>
+        <v>6867254</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 38234-2025 artfynd.xlsx
+++ b/artfynd/A 38234-2025 artfynd.xlsx
@@ -1572,45 +1572,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128484488</v>
+        <v>128485668</v>
       </c>
       <c r="B11" t="n">
-        <v>78840</v>
+        <v>98571</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467296</v>
+        <v>467380</v>
       </c>
       <c r="R11" t="n">
-        <v>6867571</v>
+        <v>6867346</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,54 +1678,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128485668</v>
+        <v>128484488</v>
       </c>
       <c r="B12" t="n">
-        <v>98571</v>
+        <v>78840</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467380</v>
+        <v>467296</v>
       </c>
       <c r="R12" t="n">
-        <v>6867346</v>
+        <v>6867571</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2569,10 +2569,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128484624</v>
+        <v>128484929</v>
       </c>
       <c r="B21" t="n">
-        <v>78841</v>
+        <v>78749</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2580,21 +2580,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467372</v>
+        <v>467411</v>
       </c>
       <c r="R21" t="n">
-        <v>6867560</v>
+        <v>6867573</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2666,10 +2666,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128484929</v>
+        <v>128486029</v>
       </c>
       <c r="B22" t="n">
-        <v>78749</v>
+        <v>79083</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2677,21 +2677,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467411</v>
+        <v>467343</v>
       </c>
       <c r="R22" t="n">
-        <v>6867573</v>
+        <v>6867360</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2763,10 +2763,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128486029</v>
+        <v>128484624</v>
       </c>
       <c r="B23" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2774,21 +2774,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467343</v>
+        <v>467372</v>
       </c>
       <c r="R23" t="n">
-        <v>6867360</v>
+        <v>6867560</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 38234-2025 artfynd.xlsx
+++ b/artfynd/A 38234-2025 artfynd.xlsx
@@ -1372,7 +1372,7 @@
         <v>128486152</v>
       </c>
       <c r="B9" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128484618</v>
       </c>
       <c r="B10" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128485668</v>
       </c>
       <c r="B11" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>128484488</v>
       </c>
       <c r="B12" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>128484498</v>
       </c>
       <c r="B13" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>128485709</v>
       </c>
       <c r="B14" t="n">
-        <v>78749</v>
+        <v>78753</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>128486130</v>
       </c>
       <c r="B15" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>128485715</v>
       </c>
       <c r="B16" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>128484758</v>
       </c>
       <c r="B17" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>128486214</v>
       </c>
       <c r="B18" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>128485871</v>
       </c>
       <c r="B19" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>128486103</v>
       </c>
       <c r="B20" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2569,10 +2569,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128484929</v>
+        <v>128484624</v>
       </c>
       <c r="B21" t="n">
-        <v>78749</v>
+        <v>78845</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2580,21 +2580,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467411</v>
+        <v>467372</v>
       </c>
       <c r="R21" t="n">
-        <v>6867573</v>
+        <v>6867560</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2666,10 +2666,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128486029</v>
+        <v>128484929</v>
       </c>
       <c r="B22" t="n">
-        <v>79083</v>
+        <v>78753</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2677,21 +2677,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467343</v>
+        <v>467411</v>
       </c>
       <c r="R22" t="n">
-        <v>6867360</v>
+        <v>6867573</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2763,10 +2763,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128484624</v>
+        <v>128486029</v>
       </c>
       <c r="B23" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2774,21 +2774,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467372</v>
+        <v>467343</v>
       </c>
       <c r="R23" t="n">
-        <v>6867560</v>
+        <v>6867360</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2863,7 +2863,7 @@
         <v>128485651</v>
       </c>
       <c r="B24" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>128486074</v>
       </c>
       <c r="B25" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>128485883</v>
       </c>
       <c r="B26" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>128484700</v>
       </c>
       <c r="B27" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>128486009</v>
       </c>
       <c r="B28" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>128485750</v>
       </c>
       <c r="B29" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>128518797</v>
       </c>
       <c r="B30" t="n">
-        <v>78749</v>
+        <v>78753</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3566,10 +3566,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128519134</v>
+        <v>128518939</v>
       </c>
       <c r="B31" t="n">
-        <v>78841</v>
+        <v>78753</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3577,21 +3577,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467662</v>
+        <v>467658</v>
       </c>
       <c r="R31" t="n">
-        <v>6867285</v>
+        <v>6867254</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3663,10 +3663,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128518939</v>
+        <v>128519134</v>
       </c>
       <c r="B32" t="n">
-        <v>78749</v>
+        <v>78845</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3674,21 +3674,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467658</v>
+        <v>467662</v>
       </c>
       <c r="R32" t="n">
-        <v>6867254</v>
+        <v>6867285</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3763,7 +3763,7 @@
         <v>128519551</v>
       </c>
       <c r="B33" t="n">
-        <v>79673</v>
+        <v>79677</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>128518723</v>
       </c>
       <c r="B34" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>128520449</v>
       </c>
       <c r="B35" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>128518707</v>
       </c>
       <c r="B36" t="n">
-        <v>78749</v>
+        <v>78753</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>128518947</v>
       </c>
       <c r="B37" t="n">
-        <v>79673</v>
+        <v>79677</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>128519150</v>
       </c>
       <c r="B38" t="n">
-        <v>79673</v>
+        <v>79677</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>128519428</v>
       </c>
       <c r="B39" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 38234-2025 artfynd.xlsx
+++ b/artfynd/A 38234-2025 artfynd.xlsx
@@ -1372,7 +1372,7 @@
         <v>128486152</v>
       </c>
       <c r="B9" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,54 +1572,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128485668</v>
+        <v>128484488</v>
       </c>
       <c r="B11" t="n">
-        <v>98579</v>
+        <v>78844</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467380</v>
+        <v>467296</v>
       </c>
       <c r="R11" t="n">
-        <v>6867346</v>
+        <v>6867571</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,45 +1669,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128484488</v>
+        <v>128485668</v>
       </c>
       <c r="B12" t="n">
-        <v>78844</v>
+        <v>98585</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467296</v>
+        <v>467380</v>
       </c>
       <c r="R12" t="n">
-        <v>6867571</v>
+        <v>6867346</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1872,45 +1872,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128485709</v>
+        <v>128484758</v>
       </c>
       <c r="B14" t="n">
-        <v>78753</v>
+        <v>98585</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467387</v>
+        <v>467386</v>
       </c>
       <c r="R14" t="n">
-        <v>6867345</v>
+        <v>6867534</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,10 +1978,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128486130</v>
+        <v>128485709</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>78753</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1980,21 +1989,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2004,10 +2013,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467340</v>
+        <v>467387</v>
       </c>
       <c r="R15" t="n">
-        <v>6867393</v>
+        <v>6867345</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2066,32 +2075,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128485715</v>
+        <v>128486130</v>
       </c>
       <c r="B16" t="n">
-        <v>98579</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2101,10 +2110,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467371</v>
+        <v>467340</v>
       </c>
       <c r="R16" t="n">
-        <v>6867346</v>
+        <v>6867393</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2163,10 +2172,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128484758</v>
+        <v>128485715</v>
       </c>
       <c r="B17" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,26 +2200,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467386</v>
+        <v>467371</v>
       </c>
       <c r="R17" t="n">
-        <v>6867534</v>
+        <v>6867346</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2369,7 +2369,7 @@
         <v>128485871</v>
       </c>
       <c r="B19" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2569,10 +2569,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128484624</v>
+        <v>128484929</v>
       </c>
       <c r="B21" t="n">
-        <v>78845</v>
+        <v>78753</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2580,21 +2580,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467372</v>
+        <v>467411</v>
       </c>
       <c r="R21" t="n">
-        <v>6867560</v>
+        <v>6867573</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2666,10 +2666,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128484929</v>
+        <v>128486029</v>
       </c>
       <c r="B22" t="n">
-        <v>78753</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2677,21 +2677,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467411</v>
+        <v>467343</v>
       </c>
       <c r="R22" t="n">
-        <v>6867573</v>
+        <v>6867360</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2763,10 +2763,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128486029</v>
+        <v>128484624</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2774,21 +2774,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467343</v>
+        <v>467372</v>
       </c>
       <c r="R23" t="n">
-        <v>6867360</v>
+        <v>6867560</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2863,7 +2863,7 @@
         <v>128485651</v>
       </c>
       <c r="B24" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>128486074</v>
       </c>
       <c r="B25" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>128485883</v>
       </c>
       <c r="B26" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>128484700</v>
       </c>
       <c r="B27" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>128485750</v>
       </c>
       <c r="B29" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 38234-2025 artfynd.xlsx
+++ b/artfynd/A 38234-2025 artfynd.xlsx
@@ -1872,54 +1872,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128484758</v>
+        <v>128485709</v>
       </c>
       <c r="B14" t="n">
-        <v>98585</v>
+        <v>78753</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467386</v>
+        <v>467387</v>
       </c>
       <c r="R14" t="n">
-        <v>6867534</v>
+        <v>6867345</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1978,10 +1969,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128485709</v>
+        <v>128486130</v>
       </c>
       <c r="B15" t="n">
-        <v>78753</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1989,21 +1980,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2013,10 +2004,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467387</v>
+        <v>467340</v>
       </c>
       <c r="R15" t="n">
-        <v>6867345</v>
+        <v>6867393</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2075,32 +2066,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128486130</v>
+        <v>128485715</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>98585</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2110,10 +2101,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467340</v>
+        <v>467371</v>
       </c>
       <c r="R16" t="n">
-        <v>6867393</v>
+        <v>6867346</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2172,7 +2163,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128485715</v>
+        <v>128484758</v>
       </c>
       <c r="B17" t="n">
         <v>98585</v>
@@ -2200,17 +2191,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467371</v>
+        <v>467386</v>
       </c>
       <c r="R17" t="n">
-        <v>6867346</v>
+        <v>6867534</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 38234-2025 artfynd.xlsx
+++ b/artfynd/A 38234-2025 artfynd.xlsx
@@ -1372,7 +1372,7 @@
         <v>128486152</v>
       </c>
       <c r="B9" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128484618</v>
       </c>
       <c r="B10" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128484488</v>
       </c>
       <c r="B11" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>128485668</v>
       </c>
       <c r="B12" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>128484498</v>
       </c>
       <c r="B13" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>128485709</v>
       </c>
       <c r="B14" t="n">
-        <v>78753</v>
+        <v>78755</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>128486130</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>128485715</v>
       </c>
       <c r="B16" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>128484758</v>
       </c>
       <c r="B17" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>128486214</v>
       </c>
       <c r="B18" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>128485871</v>
       </c>
       <c r="B19" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>128486103</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>128484929</v>
       </c>
       <c r="B21" t="n">
-        <v>78753</v>
+        <v>78755</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>128486029</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>128484624</v>
       </c>
       <c r="B23" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>128485651</v>
       </c>
       <c r="B24" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>128486074</v>
       </c>
       <c r="B25" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>128485883</v>
       </c>
       <c r="B26" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>128484700</v>
       </c>
       <c r="B27" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3266,45 +3266,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128486009</v>
+        <v>128485750</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>98588</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467344</v>
+        <v>467374</v>
       </c>
       <c r="R28" t="n">
-        <v>6867344</v>
+        <v>6867328</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3363,54 +3372,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128485750</v>
+        <v>128486009</v>
       </c>
       <c r="B29" t="n">
-        <v>98585</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467374</v>
+        <v>467344</v>
       </c>
       <c r="R29" t="n">
-        <v>6867328</v>
+        <v>6867344</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3472,7 +3472,7 @@
         <v>128518797</v>
       </c>
       <c r="B30" t="n">
-        <v>78753</v>
+        <v>78755</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>128518939</v>
       </c>
       <c r="B31" t="n">
-        <v>78753</v>
+        <v>78755</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>128519134</v>
       </c>
       <c r="B32" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>128519551</v>
       </c>
       <c r="B33" t="n">
-        <v>79677</v>
+        <v>79679</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>128520449</v>
       </c>
       <c r="B35" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>128518707</v>
       </c>
       <c r="B36" t="n">
-        <v>78753</v>
+        <v>78755</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>128518947</v>
       </c>
       <c r="B37" t="n">
-        <v>79677</v>
+        <v>79679</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>128519150</v>
       </c>
       <c r="B38" t="n">
-        <v>79677</v>
+        <v>79679</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 38234-2025 artfynd.xlsx
+++ b/artfynd/A 38234-2025 artfynd.xlsx
@@ -1372,7 +1372,7 @@
         <v>128486152</v>
       </c>
       <c r="B9" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>128485668</v>
       </c>
       <c r="B12" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,32 +1872,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128485709</v>
+        <v>128485715</v>
       </c>
       <c r="B14" t="n">
-        <v>78755</v>
+        <v>98591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467387</v>
+        <v>467371</v>
       </c>
       <c r="R14" t="n">
-        <v>6867345</v>
+        <v>6867346</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,10 +1969,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128486130</v>
+        <v>128485709</v>
       </c>
       <c r="B15" t="n">
-        <v>79089</v>
+        <v>78755</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1980,21 +1980,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467340</v>
+        <v>467387</v>
       </c>
       <c r="R15" t="n">
-        <v>6867393</v>
+        <v>6867345</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2066,32 +2066,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128485715</v>
+        <v>128486130</v>
       </c>
       <c r="B16" t="n">
-        <v>98588</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467371</v>
+        <v>467340</v>
       </c>
       <c r="R16" t="n">
-        <v>6867346</v>
+        <v>6867393</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2166,7 +2166,7 @@
         <v>128484758</v>
       </c>
       <c r="B17" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>128485871</v>
       </c>
       <c r="B19" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>128485651</v>
       </c>
       <c r="B24" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>128486074</v>
       </c>
       <c r="B25" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>128485883</v>
       </c>
       <c r="B26" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>128484700</v>
       </c>
       <c r="B27" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3266,54 +3266,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128485750</v>
+        <v>128486009</v>
       </c>
       <c r="B28" t="n">
-        <v>98588</v>
+        <v>79089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467374</v>
+        <v>467344</v>
       </c>
       <c r="R28" t="n">
-        <v>6867328</v>
+        <v>6867344</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3372,45 +3363,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128486009</v>
+        <v>128485750</v>
       </c>
       <c r="B29" t="n">
-        <v>79089</v>
+        <v>98591</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467344</v>
+        <v>467374</v>
       </c>
       <c r="R29" t="n">
-        <v>6867344</v>
+        <v>6867328</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 38234-2025 artfynd.xlsx
+++ b/artfynd/A 38234-2025 artfynd.xlsx
@@ -1572,45 +1572,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128484488</v>
+        <v>128485668</v>
       </c>
       <c r="B11" t="n">
-        <v>78846</v>
+        <v>98591</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467296</v>
+        <v>467380</v>
       </c>
       <c r="R11" t="n">
-        <v>6867571</v>
+        <v>6867346</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,54 +1678,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128485668</v>
+        <v>128484488</v>
       </c>
       <c r="B12" t="n">
-        <v>98591</v>
+        <v>78846</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467380</v>
+        <v>467296</v>
       </c>
       <c r="R12" t="n">
-        <v>6867346</v>
+        <v>6867571</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2569,10 +2569,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128484929</v>
+        <v>128484624</v>
       </c>
       <c r="B21" t="n">
-        <v>78755</v>
+        <v>78847</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2580,21 +2580,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467411</v>
+        <v>467372</v>
       </c>
       <c r="R21" t="n">
-        <v>6867573</v>
+        <v>6867560</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2666,10 +2666,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128486029</v>
+        <v>128484929</v>
       </c>
       <c r="B22" t="n">
-        <v>79089</v>
+        <v>78755</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2677,21 +2677,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467343</v>
+        <v>467411</v>
       </c>
       <c r="R22" t="n">
-        <v>6867360</v>
+        <v>6867573</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2763,10 +2763,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128484624</v>
+        <v>128486029</v>
       </c>
       <c r="B23" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2774,21 +2774,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467372</v>
+        <v>467343</v>
       </c>
       <c r="R23" t="n">
-        <v>6867560</v>
+        <v>6867360</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 38234-2025 artfynd.xlsx
+++ b/artfynd/A 38234-2025 artfynd.xlsx
@@ -1372,7 +1372,7 @@
         <v>128486152</v>
       </c>
       <c r="B9" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128485668</v>
       </c>
       <c r="B11" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128485715</v>
+        <v>128484758</v>
       </c>
       <c r="B14" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1900,17 +1900,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467371</v>
+        <v>467386</v>
       </c>
       <c r="R14" t="n">
-        <v>6867346</v>
+        <v>6867534</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2163,10 +2172,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128484758</v>
+        <v>128485715</v>
       </c>
       <c r="B17" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,26 +2200,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467386</v>
+        <v>467371</v>
       </c>
       <c r="R17" t="n">
-        <v>6867534</v>
+        <v>6867346</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2369,7 +2369,7 @@
         <v>128485871</v>
       </c>
       <c r="B19" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2569,10 +2569,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128484624</v>
+        <v>128486029</v>
       </c>
       <c r="B21" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2580,21 +2580,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467372</v>
+        <v>467343</v>
       </c>
       <c r="R21" t="n">
-        <v>6867560</v>
+        <v>6867360</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2666,10 +2666,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128484929</v>
+        <v>128484624</v>
       </c>
       <c r="B22" t="n">
-        <v>78755</v>
+        <v>78847</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2677,21 +2677,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467411</v>
+        <v>467372</v>
       </c>
       <c r="R22" t="n">
-        <v>6867573</v>
+        <v>6867560</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2763,10 +2763,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128486029</v>
+        <v>128484929</v>
       </c>
       <c r="B23" t="n">
-        <v>79089</v>
+        <v>78755</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2774,21 +2774,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467343</v>
+        <v>467411</v>
       </c>
       <c r="R23" t="n">
-        <v>6867360</v>
+        <v>6867573</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2863,7 +2863,7 @@
         <v>128485651</v>
       </c>
       <c r="B24" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>128486074</v>
       </c>
       <c r="B25" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>128485883</v>
       </c>
       <c r="B26" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>128484700</v>
       </c>
       <c r="B27" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>128485750</v>
       </c>
       <c r="B29" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3566,10 +3566,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128518939</v>
+        <v>128519134</v>
       </c>
       <c r="B31" t="n">
-        <v>78755</v>
+        <v>78847</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3577,21 +3577,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467658</v>
+        <v>467662</v>
       </c>
       <c r="R31" t="n">
-        <v>6867254</v>
+        <v>6867285</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3663,10 +3663,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128519134</v>
+        <v>128518939</v>
       </c>
       <c r="B32" t="n">
-        <v>78847</v>
+        <v>78755</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3674,21 +3674,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467662</v>
+        <v>467658</v>
       </c>
       <c r="R32" t="n">
-        <v>6867285</v>
+        <v>6867254</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 38234-2025 artfynd.xlsx
+++ b/artfynd/A 38234-2025 artfynd.xlsx
@@ -1372,7 +1372,7 @@
         <v>128486152</v>
       </c>
       <c r="B9" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128484618</v>
       </c>
       <c r="B10" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128485668</v>
       </c>
       <c r="B11" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>128484488</v>
       </c>
       <c r="B12" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>128484498</v>
       </c>
       <c r="B13" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,54 +1872,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128484758</v>
+        <v>128485709</v>
       </c>
       <c r="B14" t="n">
-        <v>98592</v>
+        <v>78782</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467386</v>
+        <v>467387</v>
       </c>
       <c r="R14" t="n">
-        <v>6867534</v>
+        <v>6867345</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1978,10 +1969,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128485709</v>
+        <v>128486130</v>
       </c>
       <c r="B15" t="n">
-        <v>78755</v>
+        <v>79116</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1989,21 +1980,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2013,10 +2004,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467387</v>
+        <v>467340</v>
       </c>
       <c r="R15" t="n">
-        <v>6867345</v>
+        <v>6867393</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2075,32 +2066,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128486130</v>
+        <v>128485715</v>
       </c>
       <c r="B16" t="n">
-        <v>79089</v>
+        <v>98619</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2110,10 +2101,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467340</v>
+        <v>467371</v>
       </c>
       <c r="R16" t="n">
-        <v>6867393</v>
+        <v>6867346</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2172,10 +2163,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128485715</v>
+        <v>128484758</v>
       </c>
       <c r="B17" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,17 +2191,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467371</v>
+        <v>467386</v>
       </c>
       <c r="R17" t="n">
-        <v>6867346</v>
+        <v>6867534</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2272,7 +2272,7 @@
         <v>128486214</v>
       </c>
       <c r="B18" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>128485871</v>
       </c>
       <c r="B19" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>128486103</v>
       </c>
       <c r="B20" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2569,10 +2569,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128486029</v>
+        <v>128484929</v>
       </c>
       <c r="B21" t="n">
-        <v>79089</v>
+        <v>78782</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2580,21 +2580,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467343</v>
+        <v>467411</v>
       </c>
       <c r="R21" t="n">
-        <v>6867360</v>
+        <v>6867573</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2666,10 +2666,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128484624</v>
+        <v>128486029</v>
       </c>
       <c r="B22" t="n">
-        <v>78847</v>
+        <v>79116</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2677,21 +2677,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467372</v>
+        <v>467343</v>
       </c>
       <c r="R22" t="n">
-        <v>6867560</v>
+        <v>6867360</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2763,10 +2763,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128484929</v>
+        <v>128484624</v>
       </c>
       <c r="B23" t="n">
-        <v>78755</v>
+        <v>78874</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2774,21 +2774,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467411</v>
+        <v>467372</v>
       </c>
       <c r="R23" t="n">
-        <v>6867573</v>
+        <v>6867560</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2863,7 +2863,7 @@
         <v>128485651</v>
       </c>
       <c r="B24" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>128486074</v>
       </c>
       <c r="B25" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>128485883</v>
       </c>
       <c r="B26" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>128484700</v>
       </c>
       <c r="B27" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>128486009</v>
       </c>
       <c r="B28" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>128485750</v>
       </c>
       <c r="B29" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>128518797</v>
       </c>
       <c r="B30" t="n">
-        <v>78755</v>
+        <v>78782</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>128519134</v>
       </c>
       <c r="B31" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>128518939</v>
       </c>
       <c r="B32" t="n">
-        <v>78755</v>
+        <v>78782</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>128519551</v>
       </c>
       <c r="B33" t="n">
-        <v>79679</v>
+        <v>79706</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>128518723</v>
       </c>
       <c r="B34" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>128520449</v>
       </c>
       <c r="B35" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>128518707</v>
       </c>
       <c r="B36" t="n">
-        <v>78755</v>
+        <v>78782</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>128518947</v>
       </c>
       <c r="B37" t="n">
-        <v>79679</v>
+        <v>79706</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>128519150</v>
       </c>
       <c r="B38" t="n">
-        <v>79679</v>
+        <v>79706</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>128519428</v>
       </c>
       <c r="B39" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 38234-2025 artfynd.xlsx
+++ b/artfynd/A 38234-2025 artfynd.xlsx
@@ -1572,54 +1572,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128485668</v>
+        <v>128484488</v>
       </c>
       <c r="B11" t="n">
-        <v>98619</v>
+        <v>78873</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467380</v>
+        <v>467296</v>
       </c>
       <c r="R11" t="n">
-        <v>6867346</v>
+        <v>6867571</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,45 +1669,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128484488</v>
+        <v>128485668</v>
       </c>
       <c r="B12" t="n">
-        <v>78873</v>
+        <v>98619</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467296</v>
+        <v>467380</v>
       </c>
       <c r="R12" t="n">
-        <v>6867571</v>
+        <v>6867346</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1872,32 +1872,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128485709</v>
+        <v>128485715</v>
       </c>
       <c r="B14" t="n">
-        <v>78782</v>
+        <v>98619</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467387</v>
+        <v>467371</v>
       </c>
       <c r="R14" t="n">
-        <v>6867345</v>
+        <v>6867346</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,45 +1969,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128486130</v>
+        <v>128484758</v>
       </c>
       <c r="B15" t="n">
-        <v>79116</v>
+        <v>98619</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467340</v>
+        <v>467386</v>
       </c>
       <c r="R15" t="n">
-        <v>6867393</v>
+        <v>6867534</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2066,32 +2075,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128485715</v>
+        <v>128485709</v>
       </c>
       <c r="B16" t="n">
-        <v>98619</v>
+        <v>78782</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2101,10 +2110,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467371</v>
+        <v>467387</v>
       </c>
       <c r="R16" t="n">
-        <v>6867346</v>
+        <v>6867345</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2163,54 +2172,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128484758</v>
+        <v>128486130</v>
       </c>
       <c r="B17" t="n">
-        <v>98619</v>
+        <v>79116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467386</v>
+        <v>467340</v>
       </c>
       <c r="R17" t="n">
-        <v>6867534</v>
+        <v>6867393</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3063,7 +3063,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128485883</v>
+        <v>128484700</v>
       </c>
       <c r="B26" t="n">
         <v>98619</v>
@@ -3091,17 +3091,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467348</v>
+        <v>467385</v>
       </c>
       <c r="R26" t="n">
-        <v>6867319</v>
+        <v>6867556</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3160,7 +3169,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128484700</v>
+        <v>128485883</v>
       </c>
       <c r="B27" t="n">
         <v>98619</v>
@@ -3188,26 +3197,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467385</v>
+        <v>467348</v>
       </c>
       <c r="R27" t="n">
-        <v>6867556</v>
+        <v>6867319</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3266,45 +3266,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128486009</v>
+        <v>128485750</v>
       </c>
       <c r="B28" t="n">
-        <v>79116</v>
+        <v>98619</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467344</v>
+        <v>467374</v>
       </c>
       <c r="R28" t="n">
-        <v>6867344</v>
+        <v>6867328</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3363,54 +3372,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128485750</v>
+        <v>128486009</v>
       </c>
       <c r="B29" t="n">
-        <v>98619</v>
+        <v>79116</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467374</v>
+        <v>467344</v>
       </c>
       <c r="R29" t="n">
-        <v>6867328</v>
+        <v>6867344</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 38234-2025 artfynd.xlsx
+++ b/artfynd/A 38234-2025 artfynd.xlsx
@@ -1372,7 +1372,7 @@
         <v>128486152</v>
       </c>
       <c r="B9" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128484618</v>
       </c>
       <c r="B10" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128484488</v>
       </c>
       <c r="B11" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>128485668</v>
       </c>
       <c r="B12" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>128484498</v>
       </c>
       <c r="B13" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>128485715</v>
       </c>
       <c r="B14" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>128484758</v>
       </c>
       <c r="B15" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>128485709</v>
       </c>
       <c r="B16" t="n">
-        <v>78782</v>
+        <v>78786</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>128486130</v>
       </c>
       <c r="B17" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>128486214</v>
       </c>
       <c r="B18" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>128485871</v>
       </c>
       <c r="B19" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>128486103</v>
       </c>
       <c r="B20" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>128484929</v>
       </c>
       <c r="B21" t="n">
-        <v>78782</v>
+        <v>78786</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>128486029</v>
       </c>
       <c r="B22" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>128484624</v>
       </c>
       <c r="B23" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>128485651</v>
       </c>
       <c r="B24" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>128486074</v>
       </c>
       <c r="B25" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3063,10 +3063,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128484700</v>
+        <v>128485883</v>
       </c>
       <c r="B26" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3091,26 +3091,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467385</v>
+        <v>467348</v>
       </c>
       <c r="R26" t="n">
-        <v>6867556</v>
+        <v>6867319</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3169,10 +3160,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128485883</v>
+        <v>128484700</v>
       </c>
       <c r="B27" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3197,17 +3188,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467348</v>
+        <v>467385</v>
       </c>
       <c r="R27" t="n">
-        <v>6867319</v>
+        <v>6867556</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3266,54 +3266,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128485750</v>
+        <v>128486009</v>
       </c>
       <c r="B28" t="n">
-        <v>98619</v>
+        <v>79120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467374</v>
+        <v>467344</v>
       </c>
       <c r="R28" t="n">
-        <v>6867328</v>
+        <v>6867344</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3372,45 +3363,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128486009</v>
+        <v>128485750</v>
       </c>
       <c r="B29" t="n">
-        <v>79116</v>
+        <v>98625</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467344</v>
+        <v>467374</v>
       </c>
       <c r="R29" t="n">
-        <v>6867344</v>
+        <v>6867328</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3472,7 +3472,7 @@
         <v>128518797</v>
       </c>
       <c r="B30" t="n">
-        <v>78782</v>
+        <v>78786</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3566,10 +3566,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128519134</v>
+        <v>128518939</v>
       </c>
       <c r="B31" t="n">
-        <v>78874</v>
+        <v>78786</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3577,21 +3577,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467662</v>
+        <v>467658</v>
       </c>
       <c r="R31" t="n">
-        <v>6867285</v>
+        <v>6867254</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3663,10 +3663,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128518939</v>
+        <v>128519134</v>
       </c>
       <c r="B32" t="n">
-        <v>78782</v>
+        <v>78878</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3674,21 +3674,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467658</v>
+        <v>467662</v>
       </c>
       <c r="R32" t="n">
-        <v>6867254</v>
+        <v>6867285</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3763,7 +3763,7 @@
         <v>128519551</v>
       </c>
       <c r="B33" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>128520449</v>
       </c>
       <c r="B35" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>128518707</v>
       </c>
       <c r="B36" t="n">
-        <v>78782</v>
+        <v>78786</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>128518947</v>
       </c>
       <c r="B37" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>128519150</v>
       </c>
       <c r="B38" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 38234-2025 artfynd.xlsx
+++ b/artfynd/A 38234-2025 artfynd.xlsx
@@ -1372,7 +1372,7 @@
         <v>128486152</v>
       </c>
       <c r="B9" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,45 +1572,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128484488</v>
+        <v>128485668</v>
       </c>
       <c r="B11" t="n">
-        <v>78877</v>
+        <v>98632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467296</v>
+        <v>467380</v>
       </c>
       <c r="R11" t="n">
-        <v>6867571</v>
+        <v>6867346</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,54 +1678,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128485668</v>
+        <v>128484488</v>
       </c>
       <c r="B12" t="n">
-        <v>98625</v>
+        <v>78877</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467380</v>
+        <v>467296</v>
       </c>
       <c r="R12" t="n">
-        <v>6867346</v>
+        <v>6867571</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1872,32 +1872,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128485715</v>
+        <v>128485709</v>
       </c>
       <c r="B14" t="n">
-        <v>98625</v>
+        <v>78786</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467371</v>
+        <v>467387</v>
       </c>
       <c r="R14" t="n">
-        <v>6867346</v>
+        <v>6867345</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,54 +1969,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128484758</v>
+        <v>128486130</v>
       </c>
       <c r="B15" t="n">
-        <v>98625</v>
+        <v>79120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467386</v>
+        <v>467340</v>
       </c>
       <c r="R15" t="n">
-        <v>6867534</v>
+        <v>6867393</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2075,32 +2066,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128485709</v>
+        <v>128485715</v>
       </c>
       <c r="B16" t="n">
-        <v>78786</v>
+        <v>98632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2110,10 +2101,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467387</v>
+        <v>467371</v>
       </c>
       <c r="R16" t="n">
-        <v>6867345</v>
+        <v>6867346</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2172,45 +2163,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128486130</v>
+        <v>128484758</v>
       </c>
       <c r="B17" t="n">
-        <v>79120</v>
+        <v>98632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467340</v>
+        <v>467386</v>
       </c>
       <c r="R17" t="n">
-        <v>6867393</v>
+        <v>6867534</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2369,7 +2369,7 @@
         <v>128485871</v>
       </c>
       <c r="B19" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2569,10 +2569,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128484929</v>
+        <v>128486029</v>
       </c>
       <c r="B21" t="n">
-        <v>78786</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2580,21 +2580,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467411</v>
+        <v>467343</v>
       </c>
       <c r="R21" t="n">
-        <v>6867573</v>
+        <v>6867360</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2666,10 +2666,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128486029</v>
+        <v>128484929</v>
       </c>
       <c r="B22" t="n">
-        <v>79120</v>
+        <v>78786</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2677,21 +2677,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467343</v>
+        <v>467411</v>
       </c>
       <c r="R22" t="n">
-        <v>6867360</v>
+        <v>6867573</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2863,7 +2863,7 @@
         <v>128485651</v>
       </c>
       <c r="B24" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>128486074</v>
       </c>
       <c r="B25" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>128485883</v>
       </c>
       <c r="B26" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>128484700</v>
       </c>
       <c r="B27" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3266,45 +3266,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128486009</v>
+        <v>128485750</v>
       </c>
       <c r="B28" t="n">
-        <v>79120</v>
+        <v>98632</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467344</v>
+        <v>467374</v>
       </c>
       <c r="R28" t="n">
-        <v>6867344</v>
+        <v>6867328</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3363,54 +3372,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128485750</v>
+        <v>128486009</v>
       </c>
       <c r="B29" t="n">
-        <v>98625</v>
+        <v>79120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467374</v>
+        <v>467344</v>
       </c>
       <c r="R29" t="n">
-        <v>6867328</v>
+        <v>6867344</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 38234-2025 artfynd.xlsx
+++ b/artfynd/A 38234-2025 artfynd.xlsx
@@ -1969,32 +1969,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128486130</v>
+        <v>128485715</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>98632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467340</v>
+        <v>467371</v>
       </c>
       <c r="R15" t="n">
-        <v>6867393</v>
+        <v>6867346</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2066,7 +2066,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128485715</v>
+        <v>128484758</v>
       </c>
       <c r="B16" t="n">
         <v>98632</v>
@@ -2094,17 +2094,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467371</v>
+        <v>467386</v>
       </c>
       <c r="R16" t="n">
-        <v>6867346</v>
+        <v>6867534</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2163,54 +2172,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128484758</v>
+        <v>128486130</v>
       </c>
       <c r="B17" t="n">
-        <v>98632</v>
+        <v>79120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467386</v>
+        <v>467340</v>
       </c>
       <c r="R17" t="n">
-        <v>6867534</v>
+        <v>6867393</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2666,10 +2666,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128484929</v>
+        <v>128484624</v>
       </c>
       <c r="B22" t="n">
-        <v>78786</v>
+        <v>78878</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2677,21 +2677,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467411</v>
+        <v>467372</v>
       </c>
       <c r="R22" t="n">
-        <v>6867573</v>
+        <v>6867560</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2763,10 +2763,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128484624</v>
+        <v>128484929</v>
       </c>
       <c r="B23" t="n">
-        <v>78878</v>
+        <v>78786</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2774,21 +2774,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467372</v>
+        <v>467411</v>
       </c>
       <c r="R23" t="n">
-        <v>6867560</v>
+        <v>6867573</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3063,7 +3063,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128485883</v>
+        <v>128484700</v>
       </c>
       <c r="B26" t="n">
         <v>98632</v>
@@ -3091,17 +3091,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467348</v>
+        <v>467385</v>
       </c>
       <c r="R26" t="n">
-        <v>6867319</v>
+        <v>6867556</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3160,7 +3169,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128484700</v>
+        <v>128485883</v>
       </c>
       <c r="B27" t="n">
         <v>98632</v>
@@ -3188,26 +3197,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467385</v>
+        <v>467348</v>
       </c>
       <c r="R27" t="n">
-        <v>6867556</v>
+        <v>6867319</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3266,54 +3266,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128485750</v>
+        <v>128486009</v>
       </c>
       <c r="B28" t="n">
-        <v>98632</v>
+        <v>79120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467374</v>
+        <v>467344</v>
       </c>
       <c r="R28" t="n">
-        <v>6867328</v>
+        <v>6867344</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3372,45 +3363,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128486009</v>
+        <v>128485750</v>
       </c>
       <c r="B29" t="n">
-        <v>79120</v>
+        <v>98632</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467344</v>
+        <v>467374</v>
       </c>
       <c r="R29" t="n">
-        <v>6867344</v>
+        <v>6867328</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 38234-2025 artfynd.xlsx
+++ b/artfynd/A 38234-2025 artfynd.xlsx
@@ -1872,10 +1872,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128485709</v>
+        <v>128486130</v>
       </c>
       <c r="B14" t="n">
-        <v>78786</v>
+        <v>79120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467387</v>
+        <v>467340</v>
       </c>
       <c r="R14" t="n">
-        <v>6867345</v>
+        <v>6867393</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,32 +1969,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128485715</v>
+        <v>128485709</v>
       </c>
       <c r="B15" t="n">
-        <v>98632</v>
+        <v>78786</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467371</v>
+        <v>467387</v>
       </c>
       <c r="R15" t="n">
-        <v>6867346</v>
+        <v>6867345</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2066,7 +2066,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128484758</v>
+        <v>128485715</v>
       </c>
       <c r="B16" t="n">
         <v>98632</v>
@@ -2094,26 +2094,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467386</v>
+        <v>467371</v>
       </c>
       <c r="R16" t="n">
-        <v>6867534</v>
+        <v>6867346</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2172,45 +2163,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128486130</v>
+        <v>128484758</v>
       </c>
       <c r="B17" t="n">
-        <v>79120</v>
+        <v>98632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467340</v>
+        <v>467386</v>
       </c>
       <c r="R17" t="n">
-        <v>6867393</v>
+        <v>6867534</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2569,10 +2569,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128486029</v>
+        <v>128484929</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>78786</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2580,21 +2580,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467343</v>
+        <v>467411</v>
       </c>
       <c r="R21" t="n">
-        <v>6867360</v>
+        <v>6867573</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2666,10 +2666,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128484624</v>
+        <v>128486029</v>
       </c>
       <c r="B22" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2677,21 +2677,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467372</v>
+        <v>467343</v>
       </c>
       <c r="R22" t="n">
-        <v>6867560</v>
+        <v>6867360</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2763,10 +2763,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128484929</v>
+        <v>128484624</v>
       </c>
       <c r="B23" t="n">
-        <v>78786</v>
+        <v>78878</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2774,21 +2774,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467411</v>
+        <v>467372</v>
       </c>
       <c r="R23" t="n">
-        <v>6867573</v>
+        <v>6867560</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3063,7 +3063,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128484700</v>
+        <v>128485883</v>
       </c>
       <c r="B26" t="n">
         <v>98632</v>
@@ -3091,26 +3091,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467385</v>
+        <v>467348</v>
       </c>
       <c r="R26" t="n">
-        <v>6867556</v>
+        <v>6867319</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3169,7 +3160,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128485883</v>
+        <v>128484700</v>
       </c>
       <c r="B27" t="n">
         <v>98632</v>
@@ -3197,17 +3188,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467348</v>
+        <v>467385</v>
       </c>
       <c r="R27" t="n">
-        <v>6867319</v>
+        <v>6867556</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 38234-2025 artfynd.xlsx
+++ b/artfynd/A 38234-2025 artfynd.xlsx
@@ -1372,7 +1372,7 @@
         <v>128486152</v>
       </c>
       <c r="B9" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128484618</v>
       </c>
       <c r="B10" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,54 +1572,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128485668</v>
+        <v>128484488</v>
       </c>
       <c r="B11" t="n">
-        <v>98632</v>
+        <v>78881</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467380</v>
+        <v>467296</v>
       </c>
       <c r="R11" t="n">
-        <v>6867346</v>
+        <v>6867571</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,45 +1669,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128484488</v>
+        <v>128485668</v>
       </c>
       <c r="B12" t="n">
-        <v>78877</v>
+        <v>98636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467296</v>
+        <v>467380</v>
       </c>
       <c r="R12" t="n">
-        <v>6867571</v>
+        <v>6867346</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1778,7 +1778,7 @@
         <v>128484498</v>
       </c>
       <c r="B13" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128486130</v>
+        <v>128485709</v>
       </c>
       <c r="B14" t="n">
-        <v>79120</v>
+        <v>78790</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467340</v>
+        <v>467387</v>
       </c>
       <c r="R14" t="n">
-        <v>6867393</v>
+        <v>6867345</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,10 +1969,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128485709</v>
+        <v>128486130</v>
       </c>
       <c r="B15" t="n">
-        <v>78786</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1980,21 +1980,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467387</v>
+        <v>467340</v>
       </c>
       <c r="R15" t="n">
-        <v>6867345</v>
+        <v>6867393</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2069,7 +2069,7 @@
         <v>128485715</v>
       </c>
       <c r="B16" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>128484758</v>
       </c>
       <c r="B17" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>128486214</v>
       </c>
       <c r="B18" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>128485871</v>
       </c>
       <c r="B19" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>128486103</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>128484929</v>
       </c>
       <c r="B21" t="n">
-        <v>78786</v>
+        <v>78790</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2666,10 +2666,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128486029</v>
+        <v>128484624</v>
       </c>
       <c r="B22" t="n">
-        <v>79120</v>
+        <v>78882</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2677,21 +2677,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467343</v>
+        <v>467372</v>
       </c>
       <c r="R22" t="n">
-        <v>6867360</v>
+        <v>6867560</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2763,10 +2763,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128484624</v>
+        <v>128486029</v>
       </c>
       <c r="B23" t="n">
-        <v>78878</v>
+        <v>79124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2774,21 +2774,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467372</v>
+        <v>467343</v>
       </c>
       <c r="R23" t="n">
-        <v>6867560</v>
+        <v>6867360</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2863,7 +2863,7 @@
         <v>128485651</v>
       </c>
       <c r="B24" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>128486074</v>
       </c>
       <c r="B25" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>128485883</v>
       </c>
       <c r="B26" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>128484700</v>
       </c>
       <c r="B27" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>128486009</v>
       </c>
       <c r="B28" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>128485750</v>
       </c>
       <c r="B29" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>128518797</v>
       </c>
       <c r="B30" t="n">
-        <v>78786</v>
+        <v>78790</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>128518939</v>
       </c>
       <c r="B31" t="n">
-        <v>78786</v>
+        <v>78790</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>128519134</v>
       </c>
       <c r="B32" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>128519551</v>
       </c>
       <c r="B33" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>128518723</v>
       </c>
       <c r="B34" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>128520449</v>
       </c>
       <c r="B35" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>128518707</v>
       </c>
       <c r="B36" t="n">
-        <v>78786</v>
+        <v>78790</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>128518947</v>
       </c>
       <c r="B37" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>128519150</v>
       </c>
       <c r="B38" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>128519428</v>
       </c>
       <c r="B39" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 38234-2025 artfynd.xlsx
+++ b/artfynd/A 38234-2025 artfynd.xlsx
@@ -1572,45 +1572,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128484488</v>
+        <v>128485668</v>
       </c>
       <c r="B11" t="n">
-        <v>78881</v>
+        <v>98636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467296</v>
+        <v>467380</v>
       </c>
       <c r="R11" t="n">
-        <v>6867571</v>
+        <v>6867346</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,54 +1678,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128485668</v>
+        <v>128484488</v>
       </c>
       <c r="B12" t="n">
-        <v>98636</v>
+        <v>78881</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467380</v>
+        <v>467296</v>
       </c>
       <c r="R12" t="n">
-        <v>6867346</v>
+        <v>6867571</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2569,10 +2569,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128484929</v>
+        <v>128484624</v>
       </c>
       <c r="B21" t="n">
-        <v>78790</v>
+        <v>78882</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2580,21 +2580,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467411</v>
+        <v>467372</v>
       </c>
       <c r="R21" t="n">
-        <v>6867573</v>
+        <v>6867560</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2666,10 +2666,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128484624</v>
+        <v>128484929</v>
       </c>
       <c r="B22" t="n">
-        <v>78882</v>
+        <v>78790</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2677,21 +2677,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467372</v>
+        <v>467411</v>
       </c>
       <c r="R22" t="n">
-        <v>6867560</v>
+        <v>6867573</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 38234-2025 artfynd.xlsx
+++ b/artfynd/A 38234-2025 artfynd.xlsx
@@ -1872,32 +1872,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128485709</v>
+        <v>128485715</v>
       </c>
       <c r="B14" t="n">
-        <v>78790</v>
+        <v>98636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467387</v>
+        <v>467371</v>
       </c>
       <c r="R14" t="n">
-        <v>6867345</v>
+        <v>6867346</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,45 +1969,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128486130</v>
+        <v>128484758</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>98636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467340</v>
+        <v>467386</v>
       </c>
       <c r="R15" t="n">
-        <v>6867393</v>
+        <v>6867534</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2066,32 +2075,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128485715</v>
+        <v>128485709</v>
       </c>
       <c r="B16" t="n">
-        <v>98636</v>
+        <v>78790</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2101,10 +2110,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467371</v>
+        <v>467387</v>
       </c>
       <c r="R16" t="n">
-        <v>6867346</v>
+        <v>6867345</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2163,54 +2172,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128484758</v>
+        <v>128486130</v>
       </c>
       <c r="B17" t="n">
-        <v>98636</v>
+        <v>79124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467386</v>
+        <v>467340</v>
       </c>
       <c r="R17" t="n">
-        <v>6867534</v>
+        <v>6867393</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 38234-2025 artfynd.xlsx
+++ b/artfynd/A 38234-2025 artfynd.xlsx
@@ -1372,7 +1372,7 @@
         <v>128486152</v>
       </c>
       <c r="B9" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128484618</v>
       </c>
       <c r="B10" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,54 +1572,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128485668</v>
+        <v>128484488</v>
       </c>
       <c r="B11" t="n">
-        <v>98636</v>
+        <v>78786</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467380</v>
+        <v>467296</v>
       </c>
       <c r="R11" t="n">
-        <v>6867346</v>
+        <v>6867571</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,45 +1669,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128484488</v>
+        <v>128485668</v>
       </c>
       <c r="B12" t="n">
-        <v>78881</v>
+        <v>98643</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467296</v>
+        <v>467380</v>
       </c>
       <c r="R12" t="n">
-        <v>6867571</v>
+        <v>6867346</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1778,7 +1778,7 @@
         <v>128484498</v>
       </c>
       <c r="B13" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>128485715</v>
       </c>
       <c r="B14" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>128484758</v>
       </c>
       <c r="B15" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>128485709</v>
       </c>
       <c r="B16" t="n">
-        <v>78790</v>
+        <v>78695</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>128486130</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>128486214</v>
       </c>
       <c r="B18" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>128485871</v>
       </c>
       <c r="B19" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>128486103</v>
       </c>
       <c r="B20" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2569,10 +2569,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128484624</v>
+        <v>128486029</v>
       </c>
       <c r="B21" t="n">
-        <v>78882</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2580,21 +2580,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467372</v>
+        <v>467343</v>
       </c>
       <c r="R21" t="n">
-        <v>6867560</v>
+        <v>6867360</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2669,7 +2669,7 @@
         <v>128484929</v>
       </c>
       <c r="B22" t="n">
-        <v>78790</v>
+        <v>78695</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2763,10 +2763,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128486029</v>
+        <v>128484624</v>
       </c>
       <c r="B23" t="n">
-        <v>79124</v>
+        <v>78787</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2774,21 +2774,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467343</v>
+        <v>467372</v>
       </c>
       <c r="R23" t="n">
-        <v>6867360</v>
+        <v>6867560</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2863,7 +2863,7 @@
         <v>128485651</v>
       </c>
       <c r="B24" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>128486074</v>
       </c>
       <c r="B25" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3063,10 +3063,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128485883</v>
+        <v>128484700</v>
       </c>
       <c r="B26" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3091,17 +3091,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467348</v>
+        <v>467385</v>
       </c>
       <c r="R26" t="n">
-        <v>6867319</v>
+        <v>6867556</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3160,10 +3169,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128484700</v>
+        <v>128485883</v>
       </c>
       <c r="B27" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3188,26 +3197,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lassbodberget, Lassbodberget, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467385</v>
+        <v>467348</v>
       </c>
       <c r="R27" t="n">
-        <v>6867556</v>
+        <v>6867319</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3269,7 +3269,7 @@
         <v>128486009</v>
       </c>
       <c r="B28" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>128485750</v>
       </c>
       <c r="B29" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>128518797</v>
       </c>
       <c r="B30" t="n">
-        <v>78790</v>
+        <v>78695</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3566,10 +3566,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128518939</v>
+        <v>128519134</v>
       </c>
       <c r="B31" t="n">
-        <v>78790</v>
+        <v>78787</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3577,21 +3577,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467658</v>
+        <v>467662</v>
       </c>
       <c r="R31" t="n">
-        <v>6867254</v>
+        <v>6867285</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3663,10 +3663,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128519134</v>
+        <v>128518939</v>
       </c>
       <c r="B32" t="n">
-        <v>78882</v>
+        <v>78695</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3674,21 +3674,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467662</v>
+        <v>467658</v>
       </c>
       <c r="R32" t="n">
-        <v>6867285</v>
+        <v>6867254</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3763,7 +3763,7 @@
         <v>128519551</v>
       </c>
       <c r="B33" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>128518723</v>
       </c>
       <c r="B34" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>128520449</v>
       </c>
       <c r="B35" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>128518707</v>
       </c>
       <c r="B36" t="n">
-        <v>78790</v>
+        <v>78695</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>128518947</v>
       </c>
       <c r="B37" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>128519150</v>
       </c>
       <c r="B38" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>128519428</v>
       </c>
       <c r="B39" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 38234-2025 artfynd.xlsx
+++ b/artfynd/A 38234-2025 artfynd.xlsx
@@ -3472,7 +3472,7 @@
         <v>128518797</v>
       </c>
       <c r="B30" t="n">
-        <v>78695</v>
+        <v>78700</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>128518939</v>
       </c>
       <c r="B31" t="n">
-        <v>78695</v>
+        <v>78700</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>128519134</v>
       </c>
       <c r="B32" t="n">
-        <v>78787</v>
+        <v>78792</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>128519551</v>
       </c>
       <c r="B33" t="n">
-        <v>79619</v>
+        <v>79624</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>128520449</v>
       </c>
       <c r="B35" t="n">
-        <v>78787</v>
+        <v>78792</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>128518707</v>
       </c>
       <c r="B36" t="n">
-        <v>78695</v>
+        <v>78700</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>128518947</v>
       </c>
       <c r="B37" t="n">
-        <v>79619</v>
+        <v>79624</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>128519150</v>
       </c>
       <c r="B38" t="n">
-        <v>79619</v>
+        <v>79624</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
